--- a/Template_Data.xlsx
+++ b/Template_Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="12255" tabRatio="796" firstSheet="15" activeTab="3"/>
+    <workbookView windowWidth="14400" windowHeight="12255" tabRatio="796" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Actions" sheetId="14" r:id="rId1"/>
@@ -1291,7 +1291,7 @@
     <t>&lt;fc=F939F4&gt;&lt;fs=40&gt;Мико-Ментори&lt;/fs&gt;&lt;/fc&gt;</t>
   </si>
   <si>
-    <t>&lt;f=Myriad Pro Light;42;1;0;0;0&gt;&lt;ls=63&gt;&lt;push=0;42&gt;Захватываете отряды пехоты, которые были уничто-&lt;br&gt;жены во время наземного боя на подконтрольных вам планетах.&lt;/ls&gt;&lt;ls=50&gt;&lt;br&gt;&lt;br&gt;&lt;/ls&gt;&lt;ls=63&gt;После каждого раунда наземного боя на подконтроль-&lt;br&gt;ной вам планете бросьте 1 кубик; если результат 7 или выше, разместите 1 захваченный отряд пехоты на эту планету.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;f=Myriad Pro Light;42;1;0;0;0&gt;&lt;ls=63&gt;&lt;push=0;42&gt;Захватывайте отряды пехоты, которые были уничто-&lt;br&gt;жены во время наземного боя на подконтрольных вам планетах.&lt;/ls&gt;&lt;ls=50&gt;&lt;br&gt;&lt;br&gt;&lt;/ls&gt;&lt;ls=63&gt;После каждого раунда наземного боя на подконтроль-&lt;br&gt;ной вам планете бросьте 1 кубик; если результат 7 или выше, разместите 1 захваченный отряд пехоты на эту планету.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>Nivyn</t>
@@ -1387,7 +1387,7 @@
     <t>&lt;fc=08F5DD&gt;&lt;fs=40&gt;Вайлерианские Разорители&lt;/fs&gt;&lt;/fc&gt;</t>
   </si>
   <si>
-    <t>&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;&lt;push=0;50&gt;После того, как вы переместили 1 более кораб-&lt;br&gt;лей в активную систему, можете сбросить 1 карту действий, чтобы переместить 1 из этих кораблей в соседнюю систему, в которой нет кораблей других игроков.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;&lt;push=0;50&gt;После того, как вы переместили 1 или более кораблей в активную систему, можете сбро-&lt;br&gt;сить 1 карту действий, чтобы переместить 1 из этих кораблей в соседнюю систему, в которой нет кораблей других игроков.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>Veldyr</t>
@@ -1399,7 +1399,7 @@
     <t>&lt;fc=31CFF3&gt;&lt;fs=40&gt;Автономия Велдиров&lt;/fs&gt;&lt;/fc&gt;</t>
   </si>
   <si>
-    <t>&lt;f=Myriad Pro Light;42;1;0;0;0&gt;&lt;ls=63&gt;&lt;push=0;42&gt;В вашей родной системе расположена туманность. Попадания, наносимые отрядами в туманностях при помощи способностей и во время боевых проверок, не могут быть отменены.&lt;/ls&gt;&lt;ls=50&gt;&lt;br&gt;&lt;br&gt;&lt;/ls&gt;&lt;ls=63&gt;Когда вы пропускаете ход, разведайте родную систему, как если бы там был жетон пограничья.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;f=Myriad Pro Light;42;1;0;0;0&gt;&lt;ls=63&gt;&lt;push=0;42&gt;В вашей родной системе расположена туманность. Попадания, наносимые вашими отрядами в туман-&lt;br&gt;ностях при помощи способностей и во время боевых проверок, не могут быть отменены.&lt;/ls&gt;&lt;ls=50&gt;&lt;br&gt;&lt;br&gt;&lt;/ls&gt;&lt;ls=63&gt;Когда вы пропускаете ход, разведайте родную систему, как если бы там был жетон пограничья.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>Zelian</t>
@@ -1411,7 +1411,7 @@
     <t>&lt;fc=E81008&gt;&lt;fs=40&gt;Зелиан&lt;/fs&gt;&lt;/fc&gt;</t>
   </si>
   <si>
-    <t>&lt;f=Myriad Pro Light;42;1;0;0;0&gt;&lt;ls=63&gt;&lt;push=0;42&gt;Подконтрольные вам планеты участвуют космическом бою в системах, пока в них есть ваши корабли. Подкон-&lt;br&gt;трольная вам планета участвует в наземном бою на этой планете, пока на ней есть ваши наземные отряды. Планете нельзя присвоить попадание. Планета имеет значение боя, равное 10 минус значение ресурсов планеты.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;f=Myriad Pro Light;42;1;0;0;0&gt;&lt;ls=63&gt;&lt;push=0;42&gt;Подконтрольные вам планеты участвуют в космическом бою в системах, пока в них есть ваши корабли. Подкон-&lt;br&gt;трольная вам планета участвует в наземном бою на этой планете, пока на ней есть ваши наземные отряды. Планете нельзя присвоить попадание. Планета имеет значение боя, равное 10 минус значение ресурсов планеты.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>Exploration</t>
@@ -10023,7 +10023,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -10115,7 +10115,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -10469,7 +10468,7 @@
       <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="32" t="s">
@@ -10478,7 +10477,7 @@
       <c r="E1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="46" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11292,7 +11291,7 @@
       </c>
       <c r="D42" s="32"/>
       <c r="E42" s="32"/>
-      <c r="F42" s="47"/>
+      <c r="F42" s="46"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="32"/>
@@ -21267,7 +21266,7 @@
       <c r="L2">
         <v>6</v>
       </c>
-      <c r="M2" s="48" t="s">
+      <c r="M2" s="47" t="s">
         <v>1666</v>
       </c>
     </row>
@@ -21302,7 +21301,7 @@
       <c r="L3">
         <v>6</v>
       </c>
-      <c r="M3" s="48" t="s">
+      <c r="M3" s="47" t="s">
         <v>1666</v>
       </c>
     </row>
@@ -21337,10 +21336,10 @@
       <c r="L4">
         <v>6</v>
       </c>
-      <c r="M4" s="48" t="s">
+      <c r="M4" s="47" t="s">
         <v>1666</v>
       </c>
-      <c r="O4" s="48" t="s">
+      <c r="O4" s="47" t="s">
         <v>1673</v>
       </c>
     </row>
@@ -21372,7 +21371,7 @@
       <c r="L5">
         <v>6</v>
       </c>
-      <c r="M5" s="48" t="s">
+      <c r="M5" s="47" t="s">
         <v>1666</v>
       </c>
     </row>
@@ -21407,7 +21406,7 @@
       <c r="L6">
         <v>6</v>
       </c>
-      <c r="M6" s="48" t="s">
+      <c r="M6" s="47" t="s">
         <v>1666</v>
       </c>
     </row>
@@ -21442,7 +21441,7 @@
       <c r="L7" t="s">
         <v>1682</v>
       </c>
-      <c r="M7" s="48" t="s">
+      <c r="M7" s="47" t="s">
         <v>1666</v>
       </c>
     </row>
@@ -28402,7 +28401,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="17"/>
-      <c r="N2" s="50" t="s">
+      <c r="N2" s="49" t="s">
         <v>2056</v>
       </c>
       <c r="O2" s="17"/>
@@ -28455,7 +28454,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="17"/>
-      <c r="N3" s="50" t="s">
+      <c r="N3" s="49" t="s">
         <v>2056</v>
       </c>
       <c r="O3" s="17"/>
@@ -28508,7 +28507,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="17"/>
-      <c r="N4" s="50" t="s">
+      <c r="N4" s="49" t="s">
         <v>2056</v>
       </c>
       <c r="O4" s="17"/>
@@ -63062,13 +63061,13 @@
       <c r="F2" t="s">
         <v>2993</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="G2" s="47" t="s">
         <v>2994</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="47" t="s">
         <v>2995</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="47" t="s">
         <v>2996</v>
       </c>
       <c r="J2" t="s">
@@ -63112,13 +63111,13 @@
       <c r="F3" t="s">
         <v>3006</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="47" t="s">
         <v>2994</v>
       </c>
-      <c r="H3" s="48" t="s">
+      <c r="H3" s="47" t="s">
         <v>3007</v>
       </c>
-      <c r="I3" s="48" t="s">
+      <c r="I3" s="47" t="s">
         <v>2996</v>
       </c>
       <c r="J3" t="s">
@@ -63162,13 +63161,13 @@
       <c r="F4" t="s">
         <v>3012</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="47" t="s">
         <v>2994</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="H4" s="47" t="s">
         <v>3013</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="47" t="s">
         <v>2996</v>
       </c>
       <c r="J4" t="s">
@@ -63228,7 +63227,7 @@
       <c r="A3" t="s">
         <v>3018</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="47" t="s">
         <v>3019</v>
       </c>
     </row>
@@ -63236,7 +63235,7 @@
       <c r="A4" t="s">
         <v>3020</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="47" t="s">
         <v>3021</v>
       </c>
     </row>
@@ -63244,7 +63243,7 @@
       <c r="A5" t="s">
         <v>274</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="47" t="s">
         <v>3022</v>
       </c>
     </row>
@@ -63308,7 +63307,7 @@
       <c r="A13" t="s">
         <v>3037</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="47" t="s">
         <v>3038</v>
       </c>
     </row>
@@ -63316,7 +63315,7 @@
       <c r="A14" t="s">
         <v>784</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="47" t="s">
         <v>3039</v>
       </c>
     </row>
@@ -63324,7 +63323,7 @@
       <c r="A15" t="s">
         <v>515</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="47" t="s">
         <v>3040</v>
       </c>
     </row>
@@ -63332,7 +63331,7 @@
       <c r="A16" t="s">
         <v>794</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="47" t="s">
         <v>3041</v>
       </c>
     </row>
@@ -63340,7 +63339,7 @@
       <c r="A17" t="s">
         <v>789</v>
       </c>
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="47" t="s">
         <v>3042</v>
       </c>
     </row>
@@ -63348,7 +63347,7 @@
       <c r="A18" t="s">
         <v>799</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="47" t="s">
         <v>3043</v>
       </c>
     </row>
@@ -63356,7 +63355,7 @@
       <c r="A19" t="s">
         <v>807</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="47" t="s">
         <v>3044</v>
       </c>
     </row>
@@ -63364,7 +63363,7 @@
       <c r="A20" t="s">
         <v>810</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="47" t="s">
         <v>3045</v>
       </c>
     </row>
@@ -63372,7 +63371,7 @@
       <c r="A21" t="s">
         <v>813</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="47" t="s">
         <v>3046</v>
       </c>
     </row>
@@ -63380,7 +63379,7 @@
       <c r="A22" t="s">
         <v>516</v>
       </c>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="47" t="s">
         <v>3047</v>
       </c>
     </row>
@@ -63388,7 +63387,7 @@
       <c r="A23" t="s">
         <v>803</v>
       </c>
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="47" t="s">
         <v>3048</v>
       </c>
     </row>
@@ -63509,7 +63508,7 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="42">
+      <c r="A6" s="41">
         <v>1</v>
       </c>
       <c r="B6" s="22" t="s">
@@ -63529,7 +63528,7 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="43">
+      <c r="A7" s="42">
         <v>1</v>
       </c>
       <c r="B7" s="22" t="s">
@@ -63549,7 +63548,7 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="43">
+      <c r="A8" s="42">
         <v>1</v>
       </c>
       <c r="B8" s="22" t="s">
@@ -63609,7 +63608,7 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="43">
+      <c r="A11" s="42">
         <v>1</v>
       </c>
       <c r="B11" s="22" t="s">
@@ -63629,7 +63628,7 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="44">
+      <c r="A12" s="43">
         <v>1</v>
       </c>
       <c r="B12" s="22" t="s">
@@ -63669,7 +63668,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="44">
+      <c r="A14" s="43">
         <v>1</v>
       </c>
       <c r="B14" s="22" t="s">
@@ -63769,7 +63768,7 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="43">
+      <c r="A19" s="42">
         <v>1</v>
       </c>
       <c r="B19" s="22" t="s">
@@ -63909,7 +63908,7 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="42">
+      <c r="A26" s="41">
         <v>1</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -63949,7 +63948,7 @@
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="43">
+      <c r="A28" s="42">
         <v>1</v>
       </c>
       <c r="B28" s="22" t="s">
@@ -63989,7 +63988,7 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="44">
+      <c r="A30" s="43">
         <v>1</v>
       </c>
       <c r="B30" s="22" t="s">
@@ -64089,7 +64088,7 @@
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="45">
+      <c r="A35" s="44">
         <v>1</v>
       </c>
       <c r="B35" s="22" t="s">
@@ -64149,7 +64148,7 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="43">
+      <c r="A38" s="42">
         <v>1</v>
       </c>
       <c r="B38" s="22" t="s">
@@ -64169,7 +64168,7 @@
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="44">
+      <c r="A39" s="43">
         <v>1</v>
       </c>
       <c r="B39" s="22" t="s">
@@ -64209,7 +64208,7 @@
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="43">
+      <c r="A41" s="42">
         <v>1</v>
       </c>
       <c r="B41" s="22" t="s">
@@ -64229,7 +64228,7 @@
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="42">
+      <c r="A42" s="41">
         <v>1</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -64249,7 +64248,7 @@
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="44">
+      <c r="A43" s="43">
         <v>1</v>
       </c>
       <c r="B43" s="22" t="s">
@@ -64369,7 +64368,7 @@
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="43">
+      <c r="A49" s="42">
         <v>1</v>
       </c>
       <c r="B49" s="22" t="s">
@@ -64389,7 +64388,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="43">
+      <c r="A50" s="42">
         <v>1</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -64429,7 +64428,7 @@
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="43">
+      <c r="A52" s="42">
         <v>1</v>
       </c>
       <c r="B52" s="22" t="s">
@@ -64449,7 +64448,7 @@
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="43">
+      <c r="A53" s="42">
         <v>1</v>
       </c>
       <c r="B53" s="22" t="s">
@@ -64489,7 +64488,7 @@
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="43">
+      <c r="A55" s="42">
         <v>1</v>
       </c>
       <c r="B55" s="22" t="s">
@@ -64509,7 +64508,7 @@
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="43">
+      <c r="A56" s="42">
         <v>1</v>
       </c>
       <c r="B56" s="22" t="s">
@@ -64529,7 +64528,7 @@
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="43">
+      <c r="A57" s="42">
         <v>1</v>
       </c>
       <c r="B57" s="22" t="s">
@@ -64549,7 +64548,7 @@
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="43">
+      <c r="A58" s="42">
         <v>1</v>
       </c>
       <c r="B58" s="22" t="s">
@@ -64663,7 +64662,7 @@
       <c r="E2" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="22" t="s">
         <v>283</v>
       </c>
       <c r="G2" s="22" t="s">
@@ -64689,7 +64688,7 @@
       <c r="E3" s="22" t="s">
         <v>288</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="22" t="s">
         <v>289</v>
       </c>
       <c r="G3" s="22" t="s">
@@ -64715,7 +64714,7 @@
       <c r="E4" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="22" t="s">
         <v>294</v>
       </c>
       <c r="G4" s="22" t="s">
@@ -64741,7 +64740,7 @@
       <c r="E5" s="22" t="s">
         <v>298</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="22" t="s">
         <v>299</v>
       </c>
       <c r="G5" s="22" t="s">
@@ -64767,7 +64766,7 @@
       <c r="E6" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="22" t="s">
         <v>303</v>
       </c>
       <c r="G6" s="22" t="s">
@@ -64793,7 +64792,7 @@
       <c r="E7" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="22" t="s">
         <v>307</v>
       </c>
       <c r="G7" s="22" t="s">
@@ -64819,7 +64818,7 @@
       <c r="E8" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="22" t="s">
         <v>311</v>
       </c>
       <c r="G8" s="22" t="s">
@@ -64845,7 +64844,7 @@
       <c r="E9" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="22" t="s">
         <v>315</v>
       </c>
       <c r="G9" s="22" t="s">
@@ -64871,7 +64870,7 @@
       <c r="E10" s="22" t="s">
         <v>318</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="22" t="s">
         <v>319</v>
       </c>
       <c r="G10" s="22" t="s">
@@ -64897,7 +64896,7 @@
       <c r="E11" s="22" t="s">
         <v>322</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="22" t="s">
         <v>323</v>
       </c>
       <c r="G11" s="22" t="s">
@@ -64923,7 +64922,7 @@
       <c r="E12" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="F12" s="22" t="s">
         <v>327</v>
       </c>
       <c r="G12" s="22" t="s">
@@ -64949,7 +64948,7 @@
       <c r="E13" s="22" t="s">
         <v>330</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="F13" s="22" t="s">
         <v>331</v>
       </c>
       <c r="G13" s="22" t="s">
@@ -64975,7 +64974,7 @@
       <c r="E14" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F14" s="22" t="s">
         <v>335</v>
       </c>
       <c r="G14" s="22" t="s">
@@ -65001,7 +65000,7 @@
       <c r="E15" s="22" t="s">
         <v>338</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="22" t="s">
         <v>339</v>
       </c>
       <c r="G15" s="22" t="s">
@@ -65027,7 +65026,7 @@
       <c r="E16" s="22" t="s">
         <v>342</v>
       </c>
-      <c r="F16" s="41" t="s">
+      <c r="F16" s="22" t="s">
         <v>343</v>
       </c>
       <c r="G16" s="22" t="s">
@@ -65053,7 +65052,7 @@
       <c r="E17" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="22" t="s">
         <v>347</v>
       </c>
       <c r="G17" s="22" t="s">
@@ -65079,7 +65078,7 @@
       <c r="E18" s="22" t="s">
         <v>350</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="22" t="s">
         <v>351</v>
       </c>
       <c r="G18" s="22" t="s">
@@ -65105,7 +65104,7 @@
       <c r="E19" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="F19" s="22" t="s">
         <v>355</v>
       </c>
       <c r="G19" s="22" t="s">
@@ -65131,7 +65130,7 @@
       <c r="E20" s="22" t="s">
         <v>358</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="F20" s="22" t="s">
         <v>359</v>
       </c>
       <c r="G20" s="22" t="s">
@@ -65157,7 +65156,7 @@
       <c r="E21" s="22" t="s">
         <v>362</v>
       </c>
-      <c r="F21" s="41" t="s">
+      <c r="F21" s="22" t="s">
         <v>363</v>
       </c>
       <c r="G21" s="22" t="s">
@@ -65183,7 +65182,7 @@
       <c r="E22" s="22" t="s">
         <v>366</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="22" t="s">
         <v>367</v>
       </c>
       <c r="G22" s="22" t="s">
@@ -65209,7 +65208,7 @@
       <c r="E23" s="22" t="s">
         <v>370</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="22" t="s">
         <v>371</v>
       </c>
       <c r="G23" s="22" t="s">
@@ -65235,7 +65234,7 @@
       <c r="E24" s="22" t="s">
         <v>374</v>
       </c>
-      <c r="F24" s="41" t="s">
+      <c r="F24" s="22" t="s">
         <v>375</v>
       </c>
       <c r="G24" s="22" t="s">
@@ -65261,7 +65260,7 @@
       <c r="E25" s="22" t="s">
         <v>378</v>
       </c>
-      <c r="F25" s="41" t="s">
+      <c r="F25" s="22" t="s">
         <v>379</v>
       </c>
       <c r="G25" s="22" t="s">
@@ -65287,7 +65286,7 @@
       <c r="E26" s="22" t="s">
         <v>382</v>
       </c>
-      <c r="F26" s="41" t="s">
+      <c r="F26" s="22" t="s">
         <v>383</v>
       </c>
       <c r="G26" s="22" t="s">
@@ -65313,7 +65312,7 @@
       <c r="E27" s="22" t="s">
         <v>386</v>
       </c>
-      <c r="F27" s="41" t="s">
+      <c r="F27" s="22" t="s">
         <v>387</v>
       </c>
       <c r="G27" s="22" t="s">
@@ -65339,7 +65338,7 @@
       <c r="E28" s="22" t="s">
         <v>390</v>
       </c>
-      <c r="F28" s="41" t="s">
+      <c r="F28" s="22" t="s">
         <v>391</v>
       </c>
       <c r="G28" s="22" t="s">
@@ -65365,7 +65364,7 @@
       <c r="E29" s="22" t="s">
         <v>394</v>
       </c>
-      <c r="F29" s="41" t="s">
+      <c r="F29" s="22" t="s">
         <v>395</v>
       </c>
       <c r="G29" s="22" t="s">
@@ -65391,7 +65390,7 @@
       <c r="E30" s="22" t="s">
         <v>398</v>
       </c>
-      <c r="F30" s="41" t="s">
+      <c r="F30" s="22" t="s">
         <v>399</v>
       </c>
       <c r="G30" s="22" t="s">
@@ -65417,7 +65416,7 @@
       <c r="E31" s="22" t="s">
         <v>402</v>
       </c>
-      <c r="F31" s="41" t="s">
+      <c r="F31" s="22" t="s">
         <v>403</v>
       </c>
       <c r="G31" s="22" t="s">
@@ -65443,7 +65442,7 @@
       <c r="E32" s="22" t="s">
         <v>406</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="22" t="s">
         <v>407</v>
       </c>
       <c r="G32" s="22" t="s">
@@ -65469,7 +65468,7 @@
       <c r="E33" s="22" t="s">
         <v>410</v>
       </c>
-      <c r="F33" s="41" t="s">
+      <c r="F33" s="22" t="s">
         <v>411</v>
       </c>
       <c r="G33" s="22" t="s">
@@ -65495,7 +65494,7 @@
       <c r="E34" s="22" t="s">
         <v>414</v>
       </c>
-      <c r="F34" s="41" t="s">
+      <c r="F34" s="22" t="s">
         <v>415</v>
       </c>
       <c r="G34" s="22" t="s">
@@ -65521,7 +65520,7 @@
       <c r="E35" s="22" t="s">
         <v>418</v>
       </c>
-      <c r="F35" s="41" t="s">
+      <c r="F35" s="22" t="s">
         <v>419</v>
       </c>
       <c r="G35" s="22" t="s">
@@ -67063,13 +67062,13 @@
       <c r="M2" t="s">
         <v>526</v>
       </c>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="47" t="s">
         <v>527</v>
       </c>
-      <c r="O2" s="48" t="s">
+      <c r="O2" s="47" t="s">
         <v>528</v>
       </c>
-      <c r="P2" s="48" t="s">
+      <c r="P2" s="47" t="s">
         <v>529</v>
       </c>
       <c r="Q2" t="s">
@@ -67113,7 +67112,7 @@
       <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3" s="48" t="s">
+      <c r="K3" s="47" t="s">
         <v>538</v>
       </c>
       <c r="L3" t="s">
@@ -67122,13 +67121,13 @@
       <c r="M3" t="s">
         <v>540</v>
       </c>
-      <c r="N3" s="48" t="s">
+      <c r="N3" s="47" t="s">
         <v>541</v>
       </c>
-      <c r="O3" s="48" t="s">
+      <c r="O3" s="47" t="s">
         <v>542</v>
       </c>
-      <c r="P3" s="48" t="s">
+      <c r="P3" s="47" t="s">
         <v>543</v>
       </c>
       <c r="Q3" t="s">
@@ -67227,7 +67226,7 @@
       <c r="J6">
         <v>4</v>
       </c>
-      <c r="K6" s="48" t="s">
+      <c r="K6" s="47" t="s">
         <v>561</v>
       </c>
       <c r="L6" t="s">
@@ -67236,13 +67235,13 @@
       <c r="M6" t="s">
         <v>540</v>
       </c>
-      <c r="N6" s="48" t="s">
+      <c r="N6" s="47" t="s">
         <v>563</v>
       </c>
-      <c r="O6" s="48" t="s">
+      <c r="O6" s="47" t="s">
         <v>564</v>
       </c>
-      <c r="P6" s="48" t="s">
+      <c r="P6" s="47" t="s">
         <v>565</v>
       </c>
       <c r="Q6" t="s">
@@ -67286,7 +67285,7 @@
       <c r="J7">
         <v>3</v>
       </c>
-      <c r="K7" s="48" t="s">
+      <c r="K7" s="47" t="s">
         <v>574</v>
       </c>
       <c r="L7" t="s">
@@ -67512,10 +67511,10 @@
       <c r="N2" t="s">
         <v>626</v>
       </c>
-      <c r="P2" s="48" t="s">
+      <c r="P2" s="47" t="s">
         <v>627</v>
       </c>
-      <c r="AK2" s="48" t="s">
+      <c r="AK2" s="47" t="s">
         <v>628</v>
       </c>
     </row>
@@ -67562,10 +67561,10 @@
       <c r="N3" t="s">
         <v>630</v>
       </c>
-      <c r="P3" s="48" t="s">
+      <c r="P3" s="47" t="s">
         <v>627</v>
       </c>
-      <c r="AK3" s="48" t="s">
+      <c r="AK3" s="47" t="s">
         <v>628</v>
       </c>
     </row>
@@ -67612,10 +67611,10 @@
       <c r="N4" t="s">
         <v>626</v>
       </c>
-      <c r="P4" s="48" t="s">
+      <c r="P4" s="47" t="s">
         <v>627</v>
       </c>
-      <c r="AK4" s="48" t="s">
+      <c r="AK4" s="47" t="s">
         <v>628</v>
       </c>
     </row>
@@ -67662,10 +67661,10 @@
       <c r="N5" t="s">
         <v>630</v>
       </c>
-      <c r="P5" s="48" t="s">
+      <c r="P5" s="47" t="s">
         <v>627</v>
       </c>
-      <c r="AK5" s="48" t="s">
+      <c r="AK5" s="47" t="s">
         <v>628</v>
       </c>
     </row>
@@ -67712,64 +67711,64 @@
       <c r="P6" t="s">
         <v>638</v>
       </c>
-      <c r="R6" s="48" t="s">
+      <c r="R6" s="47" t="s">
         <v>639</v>
       </c>
-      <c r="S6" s="48" t="s">
+      <c r="S6" s="47" t="s">
         <v>640</v>
       </c>
-      <c r="T6" s="48" t="s">
+      <c r="T6" s="47" t="s">
         <v>641</v>
       </c>
-      <c r="U6" s="48" t="s">
+      <c r="U6" s="47" t="s">
         <v>642</v>
       </c>
-      <c r="V6" s="48" t="s">
+      <c r="V6" s="47" t="s">
         <v>643</v>
       </c>
-      <c r="W6" s="48" t="s">
+      <c r="W6" s="47" t="s">
         <v>644</v>
       </c>
-      <c r="X6" s="48" t="s">
+      <c r="X6" s="47" t="s">
         <v>645</v>
       </c>
-      <c r="Y6" s="48" t="s">
+      <c r="Y6" s="47" t="s">
         <v>646</v>
       </c>
-      <c r="Z6" s="48" t="s">
+      <c r="Z6" s="47" t="s">
         <v>647</v>
       </c>
-      <c r="AA6" s="48" t="s">
+      <c r="AA6" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="AB6" s="48" t="s">
+      <c r="AB6" s="47" t="s">
         <v>649</v>
       </c>
-      <c r="AC6" s="48" t="s">
+      <c r="AC6" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="AD6" s="48" t="s">
+      <c r="AD6" s="47" t="s">
         <v>651</v>
       </c>
-      <c r="AE6" s="48" t="s">
+      <c r="AE6" s="47" t="s">
         <v>652</v>
       </c>
-      <c r="AF6" s="48" t="s">
+      <c r="AF6" s="47" t="s">
         <v>653</v>
       </c>
-      <c r="AG6" s="48" t="s">
+      <c r="AG6" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="AH6" s="48" t="s">
+      <c r="AH6" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="AI6" s="48" t="s">
+      <c r="AI6" s="47" t="s">
         <v>655</v>
       </c>
-      <c r="AJ6" s="48" t="s">
+      <c r="AJ6" s="47" t="s">
         <v>656</v>
       </c>
-      <c r="AK6" s="48" t="s">
+      <c r="AK6" s="47" t="s">
         <v>628</v>
       </c>
       <c r="AP6" t="s">
@@ -67822,61 +67821,61 @@
       <c r="P7" t="s">
         <v>638</v>
       </c>
-      <c r="R7" s="48" t="s">
+      <c r="R7" s="47" t="s">
         <v>639</v>
       </c>
-      <c r="S7" s="48" t="s">
+      <c r="S7" s="47" t="s">
         <v>640</v>
       </c>
-      <c r="T7" s="48" t="s">
+      <c r="T7" s="47" t="s">
         <v>641</v>
       </c>
-      <c r="U7" s="48" t="s">
+      <c r="U7" s="47" t="s">
         <v>642</v>
       </c>
-      <c r="V7" s="48" t="s">
+      <c r="V7" s="47" t="s">
         <v>643</v>
       </c>
-      <c r="W7" s="48" t="s">
+      <c r="W7" s="47" t="s">
         <v>644</v>
       </c>
-      <c r="X7" s="48" t="s">
+      <c r="X7" s="47" t="s">
         <v>645</v>
       </c>
-      <c r="Y7" s="48" t="s">
+      <c r="Y7" s="47" t="s">
         <v>646</v>
       </c>
-      <c r="Z7" s="48" t="s">
+      <c r="Z7" s="47" t="s">
         <v>647</v>
       </c>
-      <c r="AA7" s="48" t="s">
+      <c r="AA7" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="AB7" s="48" t="s">
+      <c r="AB7" s="47" t="s">
         <v>649</v>
       </c>
-      <c r="AC7" s="48" t="s">
+      <c r="AC7" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="AD7" s="48" t="s">
+      <c r="AD7" s="47" t="s">
         <v>651</v>
       </c>
-      <c r="AE7" s="48" t="s">
+      <c r="AE7" s="47" t="s">
         <v>652</v>
       </c>
-      <c r="AF7" s="48" t="s">
+      <c r="AF7" s="47" t="s">
         <v>653</v>
       </c>
-      <c r="AG7" s="48" t="s">
+      <c r="AG7" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="AH7" s="48" t="s">
+      <c r="AH7" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="AI7" s="48" t="s">
+      <c r="AI7" s="47" t="s">
         <v>655</v>
       </c>
-      <c r="AJ7" s="48" t="s">
+      <c r="AJ7" s="47" t="s">
         <v>656</v>
       </c>
       <c r="AK7" t="s">
@@ -67950,61 +67949,61 @@
       <c r="O8" t="s">
         <v>637</v>
       </c>
-      <c r="P8" s="48" t="s">
+      <c r="P8" s="47" t="s">
         <v>674</v>
       </c>
-      <c r="Q8" s="48" t="s">
+      <c r="Q8" s="47" t="s">
         <v>675</v>
       </c>
-      <c r="R8" s="48" t="s">
+      <c r="R8" s="47" t="s">
         <v>676</v>
       </c>
-      <c r="S8" s="48" t="s">
+      <c r="S8" s="47" t="s">
         <v>677</v>
       </c>
-      <c r="T8" s="48" t="s">
+      <c r="T8" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="U8" s="48" t="s">
+      <c r="U8" s="47" t="s">
         <v>679</v>
       </c>
-      <c r="V8" s="48" t="s">
+      <c r="V8" s="47" t="s">
         <v>680</v>
       </c>
-      <c r="W8" s="48" t="s">
+      <c r="W8" s="47" t="s">
         <v>681</v>
       </c>
-      <c r="X8" s="48" t="s">
+      <c r="X8" s="47" t="s">
         <v>647</v>
       </c>
-      <c r="AA8" s="48" t="s">
+      <c r="AA8" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="AB8" s="48" t="s">
+      <c r="AB8" s="47" t="s">
         <v>649</v>
       </c>
-      <c r="AC8" s="48" t="s">
+      <c r="AC8" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="AD8" s="48" t="s">
+      <c r="AD8" s="47" t="s">
         <v>651</v>
       </c>
-      <c r="AE8" s="48" t="s">
+      <c r="AE8" s="47" t="s">
         <v>652</v>
       </c>
-      <c r="AF8" s="48" t="s">
+      <c r="AF8" s="47" t="s">
         <v>653</v>
       </c>
-      <c r="AG8" s="48" t="s">
+      <c r="AG8" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="AH8" s="48" t="s">
+      <c r="AH8" s="47" t="s">
         <v>682</v>
       </c>
-      <c r="AI8" s="48" t="s">
+      <c r="AI8" s="47" t="s">
         <v>683</v>
       </c>
-      <c r="AJ8" s="48" t="s">
+      <c r="AJ8" s="47" t="s">
         <v>684</v>
       </c>
       <c r="AK8" t="s">
@@ -68057,7 +68056,7 @@
       <c r="Q9" t="s">
         <v>692</v>
       </c>
-      <c r="R9" s="48" t="s">
+      <c r="R9" s="47" t="s">
         <v>693</v>
       </c>
       <c r="S9" t="s">
@@ -68078,22 +68077,22 @@
       <c r="X9" t="s">
         <v>697</v>
       </c>
-      <c r="AA9" s="48" t="s">
+      <c r="AA9" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="AB9" s="48" t="s">
+      <c r="AB9" s="47" t="s">
         <v>649</v>
       </c>
-      <c r="AC9" s="48" t="s">
+      <c r="AC9" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="AD9" s="48" t="s">
+      <c r="AD9" s="47" t="s">
         <v>651</v>
       </c>
-      <c r="AE9" s="48" t="s">
+      <c r="AE9" s="47" t="s">
         <v>652</v>
       </c>
-      <c r="AF9" s="48" t="s">
+      <c r="AF9" s="47" t="s">
         <v>653</v>
       </c>
       <c r="AG9" t="s">
@@ -68111,7 +68110,7 @@
       <c r="AK9" t="s">
         <v>702</v>
       </c>
-      <c r="AR9" s="48" t="s">
+      <c r="AR9" s="47" t="s">
         <v>703</v>
       </c>
     </row>
@@ -68155,61 +68154,61 @@
       <c r="O10" t="s">
         <v>707</v>
       </c>
-      <c r="P10" s="48" t="s">
+      <c r="P10" s="47" t="s">
         <v>708</v>
       </c>
-      <c r="Q10" s="48" t="s">
+      <c r="Q10" s="47" t="s">
         <v>709</v>
       </c>
-      <c r="R10" s="48" t="s">
+      <c r="R10" s="47" t="s">
         <v>654</v>
       </c>
       <c r="S10" t="s">
         <v>677</v>
       </c>
-      <c r="T10" s="48" t="s">
+      <c r="T10" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="U10" s="48" t="s">
+      <c r="U10" s="47" t="s">
         <v>680</v>
       </c>
-      <c r="V10" s="48" t="s">
+      <c r="V10" s="47" t="s">
         <v>710</v>
       </c>
-      <c r="W10" s="48" t="s">
+      <c r="W10" s="47" t="s">
         <v>647</v>
       </c>
-      <c r="X10" s="48" t="s">
+      <c r="X10" s="47" t="s">
         <v>697</v>
       </c>
-      <c r="AA10" s="48" t="s">
+      <c r="AA10" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="AB10" s="48" t="s">
+      <c r="AB10" s="47" t="s">
         <v>649</v>
       </c>
-      <c r="AC10" s="48" t="s">
+      <c r="AC10" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="AD10" s="48" t="s">
+      <c r="AD10" s="47" t="s">
         <v>651</v>
       </c>
-      <c r="AE10" s="48" t="s">
+      <c r="AE10" s="47" t="s">
         <v>652</v>
       </c>
-      <c r="AF10" s="48" t="s">
+      <c r="AF10" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="AG10" s="48" t="s">
+      <c r="AG10" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="AH10" s="48" t="s">
+      <c r="AH10" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="AI10" s="48" t="s">
+      <c r="AI10" s="47" t="s">
         <v>654</v>
       </c>
-      <c r="AJ10" s="48" t="s">
+      <c r="AJ10" s="47" t="s">
         <v>654</v>
       </c>
       <c r="AK10" t="s">
@@ -68262,64 +68261,64 @@
       <c r="O11" t="s">
         <v>718</v>
       </c>
-      <c r="P11" s="48" t="s">
+      <c r="P11" s="47" t="s">
         <v>719</v>
       </c>
       <c r="Q11" s="38" t="s">
         <v>720</v>
       </c>
-      <c r="R11" s="49" t="s">
+      <c r="R11" s="48" t="s">
         <v>721</v>
       </c>
-      <c r="S11" s="48" t="s">
+      <c r="S11" s="47" t="s">
         <v>694</v>
       </c>
-      <c r="T11" s="48" t="s">
+      <c r="T11" s="47" t="s">
         <v>722</v>
       </c>
-      <c r="U11" s="48" t="s">
+      <c r="U11" s="47" t="s">
         <v>680</v>
       </c>
-      <c r="V11" s="48" t="s">
+      <c r="V11" s="47" t="s">
         <v>681</v>
       </c>
-      <c r="W11" s="48" t="s">
+      <c r="W11" s="47" t="s">
         <v>723</v>
       </c>
-      <c r="X11" s="48" t="s">
+      <c r="X11" s="47" t="s">
         <v>647</v>
       </c>
-      <c r="Y11" s="48" t="s">
+      <c r="Y11" s="47" t="s">
         <v>697</v>
       </c>
-      <c r="AA11" s="48" t="s">
+      <c r="AA11" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="AB11" s="48" t="s">
+      <c r="AB11" s="47" t="s">
         <v>649</v>
       </c>
-      <c r="AC11" s="48" t="s">
+      <c r="AC11" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="AD11" s="48" t="s">
+      <c r="AD11" s="47" t="s">
         <v>651</v>
       </c>
-      <c r="AE11" s="48" t="s">
+      <c r="AE11" s="47" t="s">
         <v>652</v>
       </c>
-      <c r="AF11" s="48" t="s">
+      <c r="AF11" s="47" t="s">
         <v>724</v>
       </c>
-      <c r="AG11" s="48" t="s">
+      <c r="AG11" s="47" t="s">
         <v>725</v>
       </c>
-      <c r="AH11" s="48" t="s">
+      <c r="AH11" s="47" t="s">
         <v>726</v>
       </c>
-      <c r="AI11" s="48" t="s">
+      <c r="AI11" s="47" t="s">
         <v>727</v>
       </c>
-      <c r="AJ11" s="48" t="s">
+      <c r="AJ11" s="47" t="s">
         <v>701</v>
       </c>
       <c r="AK11" t="s">
@@ -68366,61 +68365,61 @@
       <c r="O12" t="s">
         <v>733</v>
       </c>
-      <c r="P12" s="48" t="s">
+      <c r="P12" s="47" t="s">
         <v>734</v>
       </c>
       <c r="Q12" s="38" t="s">
         <v>735</v>
       </c>
-      <c r="R12" s="49" t="s">
+      <c r="R12" s="48" t="s">
         <v>736</v>
       </c>
-      <c r="S12" s="48" t="s">
+      <c r="S12" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="T12" s="48" t="s">
+      <c r="T12" s="47" t="s">
         <v>737</v>
       </c>
-      <c r="U12" s="48" t="s">
+      <c r="U12" s="47" t="s">
         <v>695</v>
       </c>
-      <c r="V12" s="48" t="s">
+      <c r="V12" s="47" t="s">
         <v>696</v>
       </c>
-      <c r="W12" s="48" t="s">
+      <c r="W12" s="47" t="s">
         <v>647</v>
       </c>
-      <c r="X12" s="48" t="s">
+      <c r="X12" s="47" t="s">
         <v>697</v>
       </c>
-      <c r="AA12" s="48" t="s">
+      <c r="AA12" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="AB12" s="48" t="s">
+      <c r="AB12" s="47" t="s">
         <v>649</v>
       </c>
-      <c r="AC12" s="48" t="s">
+      <c r="AC12" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="AD12" s="48" t="s">
+      <c r="AD12" s="47" t="s">
         <v>651</v>
       </c>
-      <c r="AE12" s="48" t="s">
+      <c r="AE12" s="47" t="s">
         <v>652</v>
       </c>
-      <c r="AF12" s="48" t="s">
+      <c r="AF12" s="47" t="s">
         <v>653</v>
       </c>
-      <c r="AG12" s="48" t="s">
+      <c r="AG12" s="47" t="s">
         <v>738</v>
       </c>
-      <c r="AH12" s="48" t="s">
+      <c r="AH12" s="47" t="s">
         <v>739</v>
       </c>
-      <c r="AI12" s="48" t="s">
+      <c r="AI12" s="47" t="s">
         <v>740</v>
       </c>
-      <c r="AJ12" s="48" t="s">
+      <c r="AJ12" s="47" t="s">
         <v>741</v>
       </c>
       <c r="AK12" t="s">
@@ -68470,58 +68469,58 @@
       <c r="O13" t="s">
         <v>747</v>
       </c>
-      <c r="P13" s="48" t="s">
+      <c r="P13" s="47" t="s">
         <v>748</v>
       </c>
       <c r="Q13" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="R13" s="48" t="s">
+      <c r="R13" s="47" t="s">
         <v>749</v>
       </c>
-      <c r="S13" s="48" t="s">
+      <c r="S13" s="47" t="s">
         <v>750</v>
       </c>
-      <c r="T13" s="48" t="s">
+      <c r="T13" s="47" t="s">
         <v>722</v>
       </c>
-      <c r="U13" s="48" t="s">
+      <c r="U13" s="47" t="s">
         <v>680</v>
       </c>
-      <c r="V13" s="48" t="s">
+      <c r="V13" s="47" t="s">
         <v>751</v>
       </c>
-      <c r="W13" s="48" t="s">
+      <c r="W13" s="47" t="s">
         <v>647</v>
       </c>
-      <c r="AA13" s="48" t="s">
+      <c r="AA13" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="AB13" s="48" t="s">
+      <c r="AB13" s="47" t="s">
         <v>649</v>
       </c>
-      <c r="AC13" s="48" t="s">
+      <c r="AC13" s="47" t="s">
         <v>650</v>
       </c>
-      <c r="AD13" s="48" t="s">
+      <c r="AD13" s="47" t="s">
         <v>651</v>
       </c>
-      <c r="AE13" s="48" t="s">
+      <c r="AE13" s="47" t="s">
         <v>652</v>
       </c>
-      <c r="AF13" s="48" t="s">
+      <c r="AF13" s="47" t="s">
         <v>653</v>
       </c>
-      <c r="AG13" s="48" t="s">
+      <c r="AG13" s="47" t="s">
         <v>752</v>
       </c>
-      <c r="AH13" s="48" t="s">
+      <c r="AH13" s="47" t="s">
         <v>753</v>
       </c>
-      <c r="AI13" s="48" t="s">
+      <c r="AI13" s="47" t="s">
         <v>754</v>
       </c>
-      <c r="AJ13" s="48" t="s">
+      <c r="AJ13" s="47" t="s">
         <v>741</v>
       </c>
       <c r="AK13" t="s">
@@ -68731,19 +68730,19 @@
       <c r="K2" t="s">
         <v>781</v>
       </c>
-      <c r="M2" s="48" t="s">
+      <c r="M2" s="47" t="s">
         <v>782</v>
       </c>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="47" t="s">
         <v>782</v>
       </c>
-      <c r="O2" s="48" t="s">
+      <c r="O2" s="47" t="s">
         <v>782</v>
       </c>
-      <c r="P2" s="48" t="s">
+      <c r="P2" s="47" t="s">
         <v>782</v>
       </c>
-      <c r="Q2" s="48" t="s">
+      <c r="Q2" s="47" t="s">
         <v>783</v>
       </c>
     </row>
@@ -68775,16 +68774,16 @@
       <c r="J3" t="s">
         <v>785</v>
       </c>
-      <c r="M3" s="48" t="s">
+      <c r="M3" s="47" t="s">
         <v>786</v>
       </c>
-      <c r="N3" s="48" t="s">
+      <c r="N3" s="47" t="s">
         <v>786</v>
       </c>
-      <c r="O3" s="48" t="s">
+      <c r="O3" s="47" t="s">
         <v>786</v>
       </c>
-      <c r="P3" s="48" t="s">
+      <c r="P3" s="47" t="s">
         <v>786</v>
       </c>
       <c r="T3" t="s">
@@ -68837,7 +68836,7 @@
       <c r="O4" t="s">
         <v>792</v>
       </c>
-      <c r="P4" s="48" t="s">
+      <c r="P4" s="47" t="s">
         <v>786</v>
       </c>
       <c r="T4" t="s">
@@ -68893,10 +68892,10 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="48" t="s">
+      <c r="Q5" s="47" t="s">
         <v>783</v>
       </c>
-      <c r="R5" s="48" t="s">
+      <c r="R5" s="47" t="s">
         <v>797</v>
       </c>
       <c r="T5" t="s">
@@ -68952,7 +68951,7 @@
       <c r="O6">
         <v>2</v>
       </c>
-      <c r="Q6" s="48" t="s">
+      <c r="Q6" s="47" t="s">
         <v>802</v>
       </c>
       <c r="T6" t="s">
@@ -68993,10 +68992,10 @@
       <c r="J7" t="s">
         <v>804</v>
       </c>
-      <c r="Q7" s="48" t="s">
+      <c r="Q7" s="47" t="s">
         <v>805</v>
       </c>
-      <c r="R7" s="48" t="s">
+      <c r="R7" s="47" t="s">
         <v>806</v>
       </c>
       <c r="T7" t="s">
@@ -69099,7 +69098,7 @@
       <c r="N9" t="s">
         <v>801</v>
       </c>
-      <c r="O9" s="48" t="s">
+      <c r="O9" s="47" t="s">
         <v>786</v>
       </c>
       <c r="T9" t="s">
@@ -69190,7 +69189,7 @@
       <c r="L11" t="s">
         <v>819</v>
       </c>
-      <c r="Q11" s="48" t="s">
+      <c r="Q11" s="47" t="s">
         <v>820</v>
       </c>
       <c r="T11" t="s">
@@ -69246,7 +69245,7 @@
       <c r="M12">
         <v>8</v>
       </c>
-      <c r="N12" s="48" t="s">
+      <c r="N12" s="47" t="s">
         <v>824</v>
       </c>
       <c r="O12">
@@ -69255,10 +69254,10 @@
       <c r="P12">
         <v>3</v>
       </c>
-      <c r="Q12" s="48" t="s">
+      <c r="Q12" s="47" t="s">
         <v>783</v>
       </c>
-      <c r="R12" s="48" t="s">
+      <c r="R12" s="47" t="s">
         <v>825</v>
       </c>
     </row>
@@ -69302,7 +69301,7 @@
       <c r="M13">
         <v>8</v>
       </c>
-      <c r="N13" s="48" t="s">
+      <c r="N13" s="47" t="s">
         <v>829</v>
       </c>
       <c r="O13">
@@ -69311,7 +69310,7 @@
       <c r="P13">
         <v>4</v>
       </c>
-      <c r="Q13" s="48" t="s">
+      <c r="Q13" s="47" t="s">
         <v>783</v>
       </c>
     </row>
@@ -69355,7 +69354,7 @@
       <c r="N14" t="s">
         <v>791</v>
       </c>
-      <c r="O14" s="48" t="s">
+      <c r="O14" s="47" t="s">
         <v>786</v>
       </c>
       <c r="T14" t="s">
@@ -69408,7 +69407,7 @@
       <c r="M15">
         <v>8</v>
       </c>
-      <c r="N15" s="48" t="s">
+      <c r="N15" s="47" t="s">
         <v>824</v>
       </c>
       <c r="O15">
@@ -69417,7 +69416,7 @@
       <c r="P15">
         <v>3</v>
       </c>
-      <c r="Q15" s="48" t="s">
+      <c r="Q15" s="47" t="s">
         <v>783</v>
       </c>
     </row>
@@ -69458,7 +69457,7 @@
       <c r="L16" t="s">
         <v>837</v>
       </c>
-      <c r="Q16" s="48" t="s">
+      <c r="Q16" s="47" t="s">
         <v>838</v>
       </c>
       <c r="T16" t="s">
@@ -69514,7 +69513,7 @@
       <c r="M17">
         <v>8</v>
       </c>
-      <c r="N17" s="48" t="s">
+      <c r="N17" s="47" t="s">
         <v>829</v>
       </c>
       <c r="O17">
@@ -69523,10 +69522,10 @@
       <c r="P17">
         <v>4</v>
       </c>
-      <c r="Q17" s="48" t="s">
+      <c r="Q17" s="47" t="s">
         <v>783</v>
       </c>
-      <c r="R17" s="48" t="s">
+      <c r="R17" s="47" t="s">
         <v>842</v>
       </c>
     </row>
@@ -69570,7 +69569,7 @@
       <c r="M18">
         <v>1</v>
       </c>
-      <c r="N18" s="48" t="s">
+      <c r="N18" s="47" t="s">
         <v>846</v>
       </c>
       <c r="O18">
@@ -69579,7 +69578,7 @@
       <c r="P18">
         <v>8</v>
       </c>
-      <c r="Q18" s="48" t="s">
+      <c r="Q18" s="47" t="s">
         <v>783</v>
       </c>
     </row>
@@ -69629,7 +69628,7 @@
       <c r="P19">
         <v>1</v>
       </c>
-      <c r="Q19" s="48" t="s">
+      <c r="Q19" s="47" t="s">
         <v>802</v>
       </c>
       <c r="T19" t="s">
@@ -69685,7 +69684,7 @@
       <c r="M20">
         <v>8</v>
       </c>
-      <c r="N20" s="48" t="s">
+      <c r="N20" s="47" t="s">
         <v>824</v>
       </c>
       <c r="O20">
@@ -69694,7 +69693,7 @@
       <c r="P20">
         <v>3</v>
       </c>
-      <c r="Q20" s="48" t="s">
+      <c r="Q20" s="47" t="s">
         <v>783</v>
       </c>
     </row>
@@ -69747,10 +69746,10 @@
       <c r="P21">
         <v>1</v>
       </c>
-      <c r="Q21" s="48" t="s">
+      <c r="Q21" s="47" t="s">
         <v>783</v>
       </c>
-      <c r="R21" s="48" t="s">
+      <c r="R21" s="47" t="s">
         <v>797</v>
       </c>
       <c r="T21" t="s">
@@ -69806,7 +69805,7 @@
       <c r="L22" t="s">
         <v>857</v>
       </c>
-      <c r="Q22" s="48" t="s">
+      <c r="Q22" s="47" t="s">
         <v>838</v>
       </c>
       <c r="T22" t="s">
@@ -69856,28 +69855,28 @@
       <c r="K29" t="s">
         <v>781</v>
       </c>
-      <c r="M29" s="48" t="s">
+      <c r="M29" s="47" t="s">
         <v>782</v>
       </c>
-      <c r="N29" s="48" t="s">
+      <c r="N29" s="47" t="s">
         <v>782</v>
       </c>
-      <c r="O29" s="48" t="s">
+      <c r="O29" s="47" t="s">
         <v>782</v>
       </c>
-      <c r="P29" s="48" t="s">
+      <c r="P29" s="47" t="s">
         <v>782</v>
       </c>
-      <c r="Q29" s="48" t="s">
+      <c r="Q29" s="47" t="s">
         <v>783</v>
       </c>
-      <c r="X29" s="48" t="s">
+      <c r="X29" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="Y29" s="48" t="s">
+      <c r="Y29" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="Z29" s="48" t="s">
+      <c r="Z29" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AA29" t="s">
@@ -69892,13 +69891,13 @@
       <c r="AD29" t="s">
         <v>631</v>
       </c>
-      <c r="AE29" s="48" t="s">
+      <c r="AE29" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AF29" s="48" t="s">
+      <c r="AF29" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AG29" s="48" t="s">
+      <c r="AG29" s="47" t="s">
         <v>631</v>
       </c>
     </row>
@@ -69939,16 +69938,16 @@
       <c r="L30" t="s">
         <v>860</v>
       </c>
-      <c r="M30" s="48" t="s">
+      <c r="M30" s="47" t="s">
         <v>786</v>
       </c>
-      <c r="N30" s="48" t="s">
+      <c r="N30" s="47" t="s">
         <v>786</v>
       </c>
-      <c r="O30" s="48" t="s">
+      <c r="O30" s="47" t="s">
         <v>786</v>
       </c>
-      <c r="P30" s="48" t="s">
+      <c r="P30" s="47" t="s">
         <v>786</v>
       </c>
       <c r="T30" t="s">
@@ -69963,13 +69962,13 @@
       <c r="W30" t="s">
         <v>788</v>
       </c>
-      <c r="X30" s="48" t="s">
+      <c r="X30" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="Y30" s="48" t="s">
+      <c r="Y30" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="Z30" s="48" t="s">
+      <c r="Z30" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AA30" t="s">
@@ -69981,16 +69980,16 @@
       <c r="AC30" t="s">
         <v>631</v>
       </c>
-      <c r="AD30" s="48" t="s">
+      <c r="AD30" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AE30" s="48" t="s">
+      <c r="AE30" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AF30" s="48" t="s">
+      <c r="AF30" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AG30" s="48" t="s">
+      <c r="AG30" s="47" t="s">
         <v>631</v>
       </c>
     </row>
@@ -70040,7 +70039,7 @@
       <c r="O31" t="s">
         <v>792</v>
       </c>
-      <c r="P31" s="48" t="s">
+      <c r="P31" s="47" t="s">
         <v>786</v>
       </c>
       <c r="T31" t="s">
@@ -70052,13 +70051,13 @@
       <c r="V31" t="s">
         <v>793</v>
       </c>
-      <c r="X31" s="48" t="s">
+      <c r="X31" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="Y31" s="48" t="s">
+      <c r="Y31" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="Z31" s="48" t="s">
+      <c r="Z31" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AA31" t="s">
@@ -70070,16 +70069,16 @@
       <c r="AC31" t="s">
         <v>631</v>
       </c>
-      <c r="AD31" s="48" t="s">
+      <c r="AD31" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AE31" s="48" t="s">
+      <c r="AE31" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AF31" s="48" t="s">
+      <c r="AF31" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AG31" s="48" t="s">
+      <c r="AG31" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AH31">
@@ -70135,10 +70134,10 @@
       <c r="P32">
         <v>1</v>
       </c>
-      <c r="Q32" s="48" t="s">
+      <c r="Q32" s="47" t="s">
         <v>783</v>
       </c>
-      <c r="R32" s="48" t="s">
+      <c r="R32" s="47" t="s">
         <v>797</v>
       </c>
       <c r="T32" t="s">
@@ -70150,13 +70149,13 @@
       <c r="V32" t="s">
         <v>798</v>
       </c>
-      <c r="X32" s="48" t="s">
+      <c r="X32" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="Y32" s="48" t="s">
+      <c r="Y32" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="Z32" s="48" t="s">
+      <c r="Z32" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AA32" t="s">
@@ -70168,16 +70167,16 @@
       <c r="AC32" t="s">
         <v>631</v>
       </c>
-      <c r="AD32" s="48" t="s">
+      <c r="AD32" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AE32" s="48" t="s">
+      <c r="AE32" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AF32" s="48" t="s">
+      <c r="AF32" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AG32" s="48" t="s">
+      <c r="AG32" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AH32">
@@ -70233,7 +70232,7 @@
       <c r="O33">
         <v>2</v>
       </c>
-      <c r="Q33" s="48" t="s">
+      <c r="Q33" s="47" t="s">
         <v>802</v>
       </c>
       <c r="T33" t="s">
@@ -70242,7 +70241,7 @@
       <c r="U33" t="s">
         <v>787</v>
       </c>
-      <c r="X33" s="48" t="s">
+      <c r="X33" s="47" t="s">
         <v>631</v>
       </c>
       <c r="Y33" t="s">
@@ -70263,13 +70262,13 @@
       <c r="AD33" t="s">
         <v>631</v>
       </c>
-      <c r="AE33" s="48" t="s">
+      <c r="AE33" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AF33" s="48" t="s">
+      <c r="AF33" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AG33" s="48" t="s">
+      <c r="AG33" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AI33">
@@ -70313,10 +70312,10 @@
       <c r="L34" t="s">
         <v>860</v>
       </c>
-      <c r="Q34" s="48" t="s">
+      <c r="Q34" s="47" t="s">
         <v>805</v>
       </c>
-      <c r="R34" s="48" t="s">
+      <c r="R34" s="47" t="s">
         <v>806</v>
       </c>
       <c r="T34" t="s">
@@ -70346,10 +70345,10 @@
       <c r="AD34" t="s">
         <v>631</v>
       </c>
-      <c r="AE34" s="48" t="s">
+      <c r="AE34" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AF34" s="48" t="s">
+      <c r="AF34" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AG34" t="s">
@@ -70408,10 +70407,10 @@
       <c r="P35">
         <v>12</v>
       </c>
-      <c r="Q35" s="48" t="s">
+      <c r="Q35" s="47" t="s">
         <v>805</v>
       </c>
-      <c r="R35" s="48" t="s">
+      <c r="R35" s="47" t="s">
         <v>806</v>
       </c>
       <c r="T35" t="s">
@@ -70441,10 +70440,10 @@
       <c r="AD35" t="s">
         <v>631</v>
       </c>
-      <c r="AE35" s="48" t="s">
+      <c r="AE35" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AF35" s="48" t="s">
+      <c r="AF35" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AG35" t="s">
@@ -70533,7 +70532,7 @@
       <c r="AD36" t="s">
         <v>631</v>
       </c>
-      <c r="AE36" s="48" t="s">
+      <c r="AE36" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AF36" t="s">
@@ -70592,7 +70591,7 @@
       <c r="N37" t="s">
         <v>801</v>
       </c>
-      <c r="O37" s="48" t="s">
+      <c r="O37" s="47" t="s">
         <v>786</v>
       </c>
       <c r="T37" t="s">
@@ -70622,7 +70621,7 @@
       <c r="AD37" t="s">
         <v>631</v>
       </c>
-      <c r="AE37" s="48" t="s">
+      <c r="AE37" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AF37" t="s">
@@ -70705,10 +70704,10 @@
       <c r="AD38" t="s">
         <v>631</v>
       </c>
-      <c r="AE38" s="48" t="s">
+      <c r="AE38" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="AF38" s="48" t="s">
+      <c r="AF38" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AG38" t="s">
@@ -70758,7 +70757,7 @@
       <c r="L39" t="s">
         <v>860</v>
       </c>
-      <c r="Q39" s="48" t="s">
+      <c r="Q39" s="47" t="s">
         <v>820</v>
       </c>
       <c r="T39" t="s">
@@ -70788,7 +70787,7 @@
       <c r="AD39" t="s">
         <v>631</v>
       </c>
-      <c r="AE39" s="48" t="s">
+      <c r="AE39" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AF39" t="s">
@@ -70874,7 +70873,7 @@
       <c r="AD40" t="s">
         <v>631</v>
       </c>
-      <c r="AE40" s="48" t="s">
+      <c r="AE40" s="47" t="s">
         <v>631</v>
       </c>
       <c r="AF40" t="s">

--- a/Template_Data.xlsx
+++ b/Template_Data.xlsx
@@ -1015,7 +1015,7 @@
     <t>Bentor</t>
   </si>
   <si>
-    <t>&lt;fs=64&gt;Кокнлав историков&lt;/fs&gt;</t>
+    <t>&lt;fs=64&gt;Конклав историков&lt;/fs&gt;</t>
   </si>
   <si>
     <t>&lt;fc=CF14EE&gt;&lt;fs=40&gt;Бенторийский Конгломерат&lt;/fs&gt;&lt;/fc&gt;</t>
@@ -1147,7 +1147,7 @@
     <t>&lt;fc=F1B823&gt;&lt;fs=30&gt;Горнодобывающий консорциум «ПРГ»&lt;/fs&gt;&lt;/fc&gt;</t>
   </si>
   <si>
-    <t>&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;&lt;push=0;50&gt;Подконтрольные вам планеты с размещённом на ней жетоном ядра считатся станциями (кроме установления контроля).&lt;/ls&gt;&lt;ls=60&gt;&lt;br&gt;&lt;br&gt;&lt;/ls&gt;&lt;ls=75&gt;Подконтрольные вам станции получают способность &lt;/f&gt;&lt;push=0;17&gt;&lt;f=Russo One;40;0;0;0;0&gt;«КОСМИЧЕСКАЯ ПУШКА 5»&lt;/f&gt;&lt;push=0;-17&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;&lt;push=0;50&gt;Подконтрольные вам планеты с размещённом на ней жетоном ядра считаются станциями (кроме установления контроля).&lt;/ls&gt;&lt;ls=60&gt;&lt;br&gt;&lt;br&gt;&lt;/ls&gt;&lt;ls=75&gt;Подконтрольные вам станции получают способность &lt;/f&gt;&lt;push=0;17&gt;&lt;f=Russo One;40;0;0;0;0&gt;«КОСМИЧЕСКАЯ ПУШКА 5»&lt;/f&gt;&lt;push=0;-17&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>Ilyxum</t>
@@ -1213,7 +1213,7 @@
     <t>Kyro</t>
   </si>
   <si>
-    <t>&lt;fs=64&gt;Расространение штамма&lt;/fs&gt;</t>
+    <t>&lt;fs=64&gt;Распространение штамма&lt;/fs&gt;</t>
   </si>
   <si>
     <t>&lt;fc=B0DE1C&gt;&lt;fs=40&gt;Община Кайро&lt;/fs&gt;&lt;/fc&gt;</t>

--- a/Template_Data.xlsx
+++ b/Template_Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" tabRatio="796" firstSheet="17" activeTab="20"/>
+    <workbookView windowWidth="19692" windowHeight="6300" tabRatio="796" firstSheet="12" activeTab="20"/>
   </bookViews>
   <sheets>
     <sheet name="Actions" sheetId="14" r:id="rId1"/>
@@ -6893,7 +6893,7 @@
     <t>&lt;fs=40&gt;Вайлерианский крейсер&lt;/fs&gt;</t>
   </si>
   <si>
-    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;Во время раунда космического боя, если ваш противник не может объявить об отступлении, он должен присвоить попадания, нанесённые этим отрядом, любым своим кораблям, кроме истребителей (при возможности). Этот отряд может перевозить только наземные отряды.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;45;1;0;0;0&gt;&lt;ls=71&gt;Во время раунда космического боя, если ваш противник не может объявить об отступлении, он должен присвоить попадания, нанесённые этим отрядом, любым своим кораблям, кроме истребителей (при возможности). Этот отряд может перевозить только наземные отряды.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>Vaylerian_icon.png</t>
@@ -6902,7 +6902,7 @@
     <t>&lt;fs=64&gt;Рейдер II&lt;/fs&gt;</t>
   </si>
   <si>
-    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;Во время раунда космического боя, если ваш противник не может объявить об отступлении, он не может отменить попадания, нанесённые этим отрядом, и должен присвоить их любым своим кораблям, кроме истребителей (при возможности).&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;44;1;0;0;0&gt;&lt;ls=71&gt;Во время раунда космического боя, если ваш противник не может объявить об отступлении, он не может отменить попадания, нанесённые этим отрядом, и должен присвоить их любым своим кораблям, кроме истребителей (при возможности).&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>Л’токк Кхраск</t>
@@ -7013,7 +7013,7 @@
     <t>&lt;fs=64&gt;Хитиновый Голиаф II&lt;/fs&gt;</t>
   </si>
   <si>
-    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;Этот отряд нельзя уничтожить картой действия «Прямое попадание».&lt;/ls&gt;&lt;ls=60&gt;&lt;br&gt;&lt;br&gt;&lt;/ls&gt;&lt;ls=75&gt;После того, как этот отряд уничтожен, вы можете разместить истребитель или эсминец из вашего снабжения в космосе системы.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;45;1;0;0;0&gt;&lt;ls=71&gt;Этот отряд нельзя уничтожить картой действия «Прямое попадание».&lt;/ls&gt;&lt;ls=52&gt;&lt;br&gt;&lt;br&gt;&lt;/ls&gt;&lt;ls=71&gt;После того, как этот отряд уничтожен, вы можете разместить истребитель или эсминец из вашего снабжения в космосе системы.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>Династия Ли-Джо</t>
@@ -7403,7 +7403,7 @@
     <t>&lt;fs=40&gt;Инструмент правосудия&lt;/fs&gt;</t>
   </si>
   <si>
-    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;&lt;/f&gt;&lt;f=Myriad Pro;50;1;0;0;0&gt;РАЗВЁРТЫВАНИЕ: &lt;/f&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;в конце вашего хода вы можете разместить этот отряд в любой системе, в которой есть ваши корабли.&lt;/ls&gt;&lt;ls=60&gt;&lt;br&gt;&lt;br&gt;&lt;/ls&gt;&lt;ls=75&gt;На этот отряд не влияют карты действий, аномалии, а также ваши фракционные способности и технологии.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;43;1;0;0;0&gt;&lt;ls=68&gt;&lt;/f&gt;&lt;f=Myriad Pro;50;1;0;0;0&gt;РАЗВЁРТЫВАНИЕ: &lt;/f&gt;&lt;f=Myriad Pro Light;43;1;0;0;0&gt;в конце вашего хода вы можете разместить этот отряд в любой системе, в которой есть ваши корабли.&lt;/ls&gt;&lt;ls=50&gt;&lt;br&gt;&lt;br&gt;&lt;/ls&gt;&lt;ls=68&gt;На этот отряд не влияют карты действий, аномалии, а также ваши фракционные способности и технологии.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>Absols_Dark</t>
@@ -7523,7 +7523,7 @@
     <t>&lt;fs=64&gt;Нечестивая мерзость II&lt;/fs&gt;</t>
   </si>
   <si>
-    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;После того, как этот отряд уничтожен, бросьте 1 кубик. Если результат броска 6 или больше, поместите отряд на эту карту. В начале вашего следующего хода разместите все отряды с этой карты на любые подконтрольные вам планеты.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;47;1;0;0;0&gt;&lt;ls=72&gt;После того, как этот отряд уничтожен, бросьте 1 кубик. Если результат броска 6 или больше, поместите отряд на эту карту. В начале вашего следующего хода разместите все отряды с этой карты на любые подконтрольные вам планеты.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>&lt;fs=64&gt;Импактор I&lt;/fs&gt;</t>
@@ -7538,7 +7538,7 @@
     <t>&lt;fs=64&gt;Импактор II&lt;/fs&gt;</t>
   </si>
   <si>
-    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;После того, как этот отряд уничтожен, бросьте 1 кубик. Если результат броска 6 или больше, поместите отряд на эту карту. В начале вашего следующего хода разместите все отряды с этой карты на подконтрольной вам планете в родной системе.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;45;1;0;0;0&gt;&lt;ls=71&gt;После того, как этот отряд уничтожен, бросьте 1 кубик. Если результат броска 6 или больше, поместите отряд на эту карту. В начале вашего следующего хода разместите все отряды с этой карты на подконтрольной вам планете в родной системе.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>&lt;fs=64&gt;Иледрит&lt;/fs&gt;</t>
@@ -7547,7 +7547,7 @@
     <t>&lt;fs=40&gt;Мех Авгуров&lt;/fs&gt;</t>
   </si>
   <si>
-    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;Переверните эту карту, чтобы разместить 2 эсминца из вашего снабжения в системе, в которой есть хотя бы 1 ваш корабль и ваш жетон приказа. В начале фазы статуса, если эта карта перевёрнута, верните её в снабжение играющего за Судостроителей Оси.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;45;1;0;0;0&gt;&lt;ls=71&gt;Переверните эту карту, чтобы разместить 2 эсминца из вашего снабжения в системе, в которой есть хотя бы 1 ваш корабль и ваш жетон приказа. В начале фазы статуса, если эта карта перевёрнута, верните её в снабжение играющего за Судостроителей Оси.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>&lt;fs=44&gt;Штормовой Призыватель Авроры&lt;/fs&gt;</t>
@@ -7628,7 +7628,7 @@
     <t>&lt;fs=40&gt;Мех Ли-Джо&lt;/fs&gt;</t>
   </si>
   <si>
-    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;В начале вашего хода вы можете убрать 1 прикрепление «Ловушка» с игрового поля и прикрепить его к этой планете, или поменять местами прикрепление «Ловушка» с этой планеты и любое другое на игровом поле.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;49;1;0;0;0&gt;&lt;ls=74&gt;В начале вашего хода вы можете убрать 1 прикрепление «Ловушка» с игрового поля и прикрепить его к этой планете, или поменять местами прикрепление «Ловушка» с этой планеты и любое другое на игровом поле.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>&lt;fs=44&gt;Хранитель Вспышки Пустоты I&lt;/fs&gt;</t>
@@ -7817,7 +7817,7 @@
     <t>&lt;fs=40&gt;Мех Содружества&lt;/fs&gt;</t>
   </si>
   <si>
-    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;&lt;ls=75&gt;&lt;/f&gt;&lt;f=Myriad Pro;50;1;0;0;0&gt;РАЗВЁРТЫВАНИЕ: &lt;/f&gt;&lt;f=Myriad Pro Light;50;1;0;0;0&gt;после того, как вы использовали фракционную способность «Ради общего блага», можете потратить 1 товар, чтобы разместить 1 меха на подконтрольной вам планете в этой или смежной системе.&lt;/ls&gt;&lt;/f&gt;</t>
+    <t>&lt;push=0;25&gt;&lt;f=Myriad Pro Light;47;1;0;0;0&gt;&lt;ls=72&gt;&lt;/f&gt;&lt;f=Myriad Pro;47;1;0;0;0&gt;РАЗВЁРТЫВАНИЕ: &lt;/f&gt;&lt;f=Myriad Pro Light;47;1;0;0;0&gt;после того, как вы использовали фракционную способность «Ради общего блага», можете потратить 1 товар, чтобы разместить 1 меха на подконтрольной вам планете в этой или смежной системе.&lt;/ls&gt;&lt;/f&gt;</t>
   </si>
   <si>
     <t>&lt;fs=64&gt;Тиолеомбп&lt;/fs&gt;</t>
@@ -41616,7 +41616,7 @@
     <col min="2" max="2" width="9.77777777777778" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.55555555555556" style="1" customWidth="1"/>
     <col min="4" max="4" width="7.55555555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1018518518519" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="8" width="12.7777777777778" style="1" customWidth="1"/>
@@ -50048,7 +50048,7 @@
         <v>366</v>
       </c>
       <c r="AE109" s="19">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:32">
@@ -50135,7 +50135,7 @@
         <v>366</v>
       </c>
       <c r="AE110" s="19">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:32">
